--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\DEV\LCARS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\DEV\LCARS-FAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83D8D9A-EF75-4F2D-BA7C-93FBDF133EC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E343CC4-547A-43E4-B02F-24B55AC19FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{10BE6906-5E43-42C5-9E7C-F0FE7B38391D}"/>
   </bookViews>
   <sheets>
-    <sheet name="bugsDB" sheetId="1" r:id="rId1"/>
+    <sheet name="toDo" sheetId="2" r:id="rId1"/>
+    <sheet name="bugsDB" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="45">
   <si>
     <t>ID</t>
   </si>
@@ -159,13 +160,28 @@
   </si>
   <si>
     <t>Al</t>
+  </si>
+  <si>
+    <t>What</t>
+  </si>
+  <si>
+    <t>Why</t>
+  </si>
+  <si>
+    <t>ID #</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Every deployment step currently requires Claude to write out exact commands, the user pastes them into a separate terminal, runs them, and pastes results back — slow, and error-prone over several round-trips (e.g. today's server.py getting silently overwritten by Application Manager took multiple manual diagnostic round-trips to catch). Key-based auth needs no password to ever be typed or seen by anyone, including Claude, so it doesn't compromise credential security — it just removes the manual relay step, letting Claude run deployments and diagnostics directly.</t>
+  </si>
+  <si>
+    <t>Generate an SSH key pair and add the public key to GoDaddy's authorized keys (cPanel → SSH Access, or ~/.ssh/authorized_keys directly), so Claude Code can run ssh/scp commands against the server itself. Then build a script that deploys the dev instance to the live GoDaddy server</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +196,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -208,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -220,6 +241,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -555,6 +579,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B97A43-702C-46A2-8F43-919E984849E9}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="124.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1D90671-FA13-41AE-9901-2C67E897E924}">
   <dimension ref="A1:M145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\DEV\LCARS-FAS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E343CC4-547A-43E4-B02F-24B55AC19FCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E5CCEF-3278-4858-81EF-29B73839BF01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{10BE6906-5E43-42C5-9E7C-F0FE7B38391D}"/>
   </bookViews>
@@ -229,7 +229,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -245,6 +245,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -580,7 +583,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B97A43-702C-46A2-8F43-919E984849E9}">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="3" width="124.28515625" customWidth="1"/>
@@ -598,7 +601,7 @@
       </c>
     </row>
     <row r="2" spans="1:3" ht="75" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -607,6 +610,826 @@
       <c r="C2" s="1" t="s">
         <v>43</v>
       </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="6"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="1"/>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="6"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="1"/>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="6"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="1"/>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="6"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="1"/>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="6"/>
+      <c r="B7" s="5"/>
+      <c r="C7" s="1"/>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="6"/>
+      <c r="B8" s="5"/>
+      <c r="C8" s="1"/>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="6"/>
+      <c r="B9" s="5"/>
+      <c r="C9" s="1"/>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="6"/>
+      <c r="B10" s="5"/>
+      <c r="C10" s="1"/>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="6"/>
+      <c r="B11" s="5"/>
+      <c r="C11" s="1"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="1"/>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="6"/>
+      <c r="B13" s="5"/>
+      <c r="C13" s="1"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="6"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="1"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="6"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="1"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6"/>
+      <c r="B16" s="5"/>
+      <c r="C16" s="1"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="1"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="6"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="1"/>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="6"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="1"/>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="6"/>
+      <c r="B20" s="5"/>
+      <c r="C20" s="1"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="6"/>
+      <c r="B21" s="5"/>
+      <c r="C21" s="1"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="6"/>
+      <c r="B22" s="5"/>
+      <c r="C22" s="1"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="6"/>
+      <c r="B23" s="5"/>
+      <c r="C23" s="1"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="6"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="1"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="6"/>
+      <c r="B25" s="5"/>
+      <c r="C25" s="1"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="6"/>
+      <c r="B26" s="5"/>
+      <c r="C26" s="1"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="6"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="1"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="6"/>
+      <c r="B28" s="5"/>
+      <c r="C28" s="1"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="6"/>
+      <c r="B29" s="5"/>
+      <c r="C29" s="1"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="6"/>
+      <c r="B30" s="5"/>
+      <c r="C30" s="1"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="6"/>
+      <c r="B31" s="5"/>
+      <c r="C31" s="1"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="6"/>
+      <c r="B32" s="5"/>
+      <c r="C32" s="1"/>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="6"/>
+      <c r="B33" s="5"/>
+      <c r="C33" s="1"/>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="6"/>
+      <c r="B34" s="5"/>
+      <c r="C34" s="1"/>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="6"/>
+      <c r="B35" s="5"/>
+      <c r="C35" s="1"/>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="6"/>
+      <c r="B36" s="5"/>
+      <c r="C36" s="1"/>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="6"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="1"/>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="6"/>
+      <c r="B38" s="5"/>
+      <c r="C38" s="1"/>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="6"/>
+      <c r="B39" s="5"/>
+      <c r="C39" s="1"/>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="6"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="1"/>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="6"/>
+      <c r="B41" s="5"/>
+      <c r="C41" s="1"/>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="6"/>
+      <c r="B42" s="5"/>
+      <c r="C42" s="1"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="6"/>
+      <c r="B43" s="5"/>
+      <c r="C43" s="1"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="6"/>
+      <c r="B44" s="5"/>
+      <c r="C44" s="1"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="6"/>
+      <c r="B45" s="5"/>
+      <c r="C45" s="1"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="6"/>
+      <c r="B46" s="5"/>
+      <c r="C46" s="1"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="6"/>
+      <c r="B47" s="5"/>
+      <c r="C47" s="1"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="6"/>
+      <c r="B48" s="5"/>
+      <c r="C48" s="1"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="6"/>
+      <c r="B49" s="5"/>
+      <c r="C49" s="1"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="6"/>
+      <c r="B50" s="5"/>
+      <c r="C50" s="1"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="6"/>
+      <c r="B51" s="5"/>
+      <c r="C51" s="1"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="6"/>
+      <c r="B52" s="5"/>
+      <c r="C52" s="1"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="6"/>
+      <c r="B53" s="5"/>
+      <c r="C53" s="1"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="6"/>
+      <c r="B54" s="5"/>
+      <c r="C54" s="1"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="6"/>
+      <c r="B55" s="5"/>
+      <c r="C55" s="1"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="6"/>
+      <c r="B56" s="5"/>
+      <c r="C56" s="1"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="6"/>
+      <c r="B57" s="5"/>
+      <c r="C57" s="1"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="6"/>
+      <c r="B58" s="5"/>
+      <c r="C58" s="1"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="6"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="1"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="6"/>
+      <c r="B60" s="5"/>
+      <c r="C60" s="1"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="6"/>
+      <c r="B61" s="5"/>
+      <c r="C61" s="1"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6"/>
+      <c r="B62" s="5"/>
+      <c r="C62" s="1"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="6"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="1"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="6"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="1"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="6"/>
+      <c r="B65" s="5"/>
+      <c r="C65" s="1"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="6"/>
+      <c r="B66" s="5"/>
+      <c r="C66" s="1"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="6"/>
+      <c r="B67" s="5"/>
+      <c r="C67" s="1"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="6"/>
+      <c r="B68" s="5"/>
+      <c r="C68" s="1"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="6"/>
+      <c r="B69" s="5"/>
+      <c r="C69" s="1"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="6"/>
+      <c r="B70" s="5"/>
+      <c r="C70" s="1"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="6"/>
+      <c r="B71" s="5"/>
+      <c r="C71" s="1"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="6"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="1"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="6"/>
+      <c r="B73" s="5"/>
+      <c r="C73" s="1"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="6"/>
+      <c r="B74" s="5"/>
+      <c r="C74" s="1"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="6"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="1"/>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="6"/>
+      <c r="B76" s="5"/>
+      <c r="C76" s="1"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="6"/>
+      <c r="B77" s="5"/>
+      <c r="C77" s="1"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="6"/>
+      <c r="B78" s="5"/>
+      <c r="C78" s="1"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="6"/>
+      <c r="B79" s="5"/>
+      <c r="C79" s="1"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="6"/>
+      <c r="B80" s="5"/>
+      <c r="C80" s="1"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="6"/>
+      <c r="B81" s="5"/>
+      <c r="C81" s="1"/>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="6"/>
+      <c r="B82" s="5"/>
+      <c r="C82" s="1"/>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="6"/>
+      <c r="B83" s="5"/>
+      <c r="C83" s="1"/>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="6"/>
+      <c r="B84" s="5"/>
+      <c r="C84" s="1"/>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="6"/>
+      <c r="B85" s="5"/>
+      <c r="C85" s="1"/>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="6"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="1"/>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="6"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="1"/>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="6"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="1"/>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="6"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="1"/>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="6"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="1"/>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="6"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="1"/>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="6"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="1"/>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="6"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="1"/>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="6"/>
+      <c r="B94" s="5"/>
+      <c r="C94" s="1"/>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="6"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="1"/>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="6"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="1"/>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="6"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="1"/>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="6"/>
+      <c r="B98" s="5"/>
+      <c r="C98" s="1"/>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="6"/>
+      <c r="B99" s="5"/>
+      <c r="C99" s="1"/>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="6"/>
+      <c r="B100" s="5"/>
+      <c r="C100" s="1"/>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="6"/>
+      <c r="B101" s="5"/>
+      <c r="C101" s="1"/>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="6"/>
+      <c r="B102" s="5"/>
+      <c r="C102" s="1"/>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="6"/>
+      <c r="B103" s="5"/>
+      <c r="C103" s="1"/>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="6"/>
+      <c r="B104" s="5"/>
+      <c r="C104" s="1"/>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="6"/>
+      <c r="B105" s="5"/>
+      <c r="C105" s="1"/>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="6"/>
+      <c r="B106" s="5"/>
+      <c r="C106" s="1"/>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="6"/>
+      <c r="B107" s="5"/>
+      <c r="C107" s="1"/>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="6"/>
+      <c r="B108" s="5"/>
+      <c r="C108" s="1"/>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="6"/>
+      <c r="B109" s="5"/>
+      <c r="C109" s="1"/>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="6"/>
+      <c r="B110" s="5"/>
+      <c r="C110" s="1"/>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="6"/>
+      <c r="B111" s="5"/>
+      <c r="C111" s="1"/>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="6"/>
+      <c r="B112" s="5"/>
+      <c r="C112" s="1"/>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="6"/>
+      <c r="B113" s="5"/>
+      <c r="C113" s="1"/>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="6"/>
+      <c r="B114" s="5"/>
+      <c r="C114" s="1"/>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="6"/>
+      <c r="B115" s="5"/>
+      <c r="C115" s="1"/>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="6"/>
+      <c r="B116" s="5"/>
+      <c r="C116" s="1"/>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="6"/>
+      <c r="B117" s="5"/>
+      <c r="C117" s="1"/>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="6"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="1"/>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="6"/>
+      <c r="B119" s="5"/>
+      <c r="C119" s="1"/>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="6"/>
+      <c r="B120" s="5"/>
+      <c r="C120" s="1"/>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="6"/>
+      <c r="B121" s="5"/>
+      <c r="C121" s="1"/>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="6"/>
+      <c r="B122" s="5"/>
+      <c r="C122" s="1"/>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="6"/>
+      <c r="B123" s="5"/>
+      <c r="C123" s="1"/>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="6"/>
+      <c r="B124" s="5"/>
+      <c r="C124" s="1"/>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="6"/>
+      <c r="B125" s="5"/>
+      <c r="C125" s="1"/>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="6"/>
+      <c r="B126" s="5"/>
+      <c r="C126" s="1"/>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="6"/>
+      <c r="B127" s="5"/>
+      <c r="C127" s="1"/>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="6"/>
+      <c r="B128" s="5"/>
+      <c r="C128" s="1"/>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="6"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="1"/>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="6"/>
+      <c r="B130" s="5"/>
+      <c r="C130" s="1"/>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="6"/>
+      <c r="B131" s="5"/>
+      <c r="C131" s="1"/>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="6"/>
+      <c r="B132" s="5"/>
+      <c r="C132" s="1"/>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="6"/>
+      <c r="B133" s="5"/>
+      <c r="C133" s="1"/>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="6"/>
+      <c r="B134" s="5"/>
+      <c r="C134" s="1"/>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="6"/>
+      <c r="B135" s="5"/>
+      <c r="C135" s="1"/>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="6"/>
+      <c r="B136" s="5"/>
+      <c r="C136" s="1"/>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="6"/>
+      <c r="B137" s="5"/>
+      <c r="C137" s="1"/>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="6"/>
+      <c r="B138" s="5"/>
+      <c r="C138" s="1"/>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="6"/>
+      <c r="B139" s="5"/>
+      <c r="C139" s="1"/>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="6"/>
+      <c r="B140" s="5"/>
+      <c r="C140" s="1"/>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="6"/>
+      <c r="B141" s="5"/>
+      <c r="C141" s="1"/>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="6"/>
+      <c r="B142" s="5"/>
+      <c r="C142" s="1"/>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="6"/>
+      <c r="B143" s="5"/>
+      <c r="C143" s="1"/>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="6"/>
+      <c r="B144" s="5"/>
+      <c r="C144" s="1"/>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="6"/>
+      <c r="B145" s="5"/>
+      <c r="C145" s="1"/>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="6"/>
+      <c r="B146" s="5"/>
+      <c r="C146" s="1"/>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="6"/>
+      <c r="B147" s="5"/>
+      <c r="C147" s="1"/>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="6"/>
+      <c r="B148" s="5"/>
+      <c r="C148" s="1"/>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="6"/>
+      <c r="B149" s="5"/>
+      <c r="C149" s="1"/>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="6"/>
+      <c r="B150" s="5"/>
+      <c r="C150" s="1"/>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="6"/>
+      <c r="B151" s="5"/>
+      <c r="C151" s="1"/>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="6"/>
+      <c r="B152" s="5"/>
+      <c r="C152" s="1"/>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="6"/>
+      <c r="B153" s="5"/>
+      <c r="C153" s="1"/>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="6"/>
+      <c r="B154" s="5"/>
+      <c r="C154" s="1"/>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="6"/>
+      <c r="B155" s="5"/>
+      <c r="C155" s="1"/>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="6"/>
+      <c r="B156" s="5"/>
+      <c r="C156" s="1"/>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="6"/>
+      <c r="B157" s="5"/>
+      <c r="C157" s="1"/>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="6"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="1"/>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="6"/>
+      <c r="B159" s="5"/>
+      <c r="C159" s="1"/>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="6"/>
+      <c r="B160" s="5"/>
+      <c r="C160" s="1"/>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="6"/>
+      <c r="B161" s="5"/>
+      <c r="C161" s="1"/>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="6"/>
+      <c r="B162" s="5"/>
+      <c r="C162" s="1"/>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="6"/>
+      <c r="B163" s="5"/>
+      <c r="C163" s="1"/>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="6"/>
+      <c r="B164" s="5"/>
+      <c r="C164" s="1"/>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="6"/>
+      <c r="B165" s="5"/>
+      <c r="C165" s="1"/>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="6"/>
+      <c r="B166" s="5"/>
+      <c r="C166" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -1297,7 +1297,7 @@
       </c>
       <c r="Q8" s="8" t="inlineStr">
         <is>
-          <t>PARTIAL FIX (2026-10-10): rewrite rules appended to public_html/LCARS-FAS/.htaccess, after the CloudLinux/Passenger blocks (original backed up to ~/backups/LCARS-FAS.htaccess.pre-bug7). They refuse (403) the scripts/, ingestionDBs/, tmp/, __pycache__/ and public/ folders, any *.py, *.pyc, *.sh, *.db (and -wal/-shm/-journal), *.bak, *.xlsx, *.env, *.example, *.log, *.tar, *.gz file, and dot-files (.git*, .env). Verified: 15 sensitive URLs now return 403; index.html, assets/ (including fonts, Leaflet and onOrbitMethodology.md) and the api/ routes still return 200. The rules are on the server only: .htaccess is excluded from deploys, so they survive redeploys but are not in git. STILL TO DO: (1) Proper fix: move the app root outside public_html (cPanel Python app setting, plus REMOTE_PATH in deployToGoDaddy.sh and APP_ROOT/PYTHON in setupCron.sh), so nothing is downloadable unless server.py serves it; the rules are a blocklist, so a new file type (say .json data) would still be public. (2) GitHub repo ajg19/LCARS-FAS is public and earlier commits still contain orbitalObjects.db (Space-Track data) and space_news.db: make the repo private, or rewrite history (irreversible, force-push). (3) Delete stale leftovers on the server (deployToGoDaddy.sh, .gitignore, orbital_rocket_families-2.xlsx, server.pyc, passenger_wsgi.pyc, __pycache__): now blocked, but not needed. (4) Keep a copy of the .htaccess rules in the repo (e.g. 0_documentation) so they can be restored if cPanel rewrites the file.</t>
+          <t>PARTIAL FIX (2026-10-10): rewrite rules appended to public_html/LCARS-FAS/.htaccess, after the CloudLinux/Passenger blocks (original backed up to ~/backups/LCARS-FAS.htaccess.pre-bug7). They refuse (403) the scripts/, ingestionDBs/, tmp/, __pycache__/ and public/ folders, any *.py, *.pyc, *.sh, *.db (and -wal/-shm/-journal), *.bak, *.xlsx, *.env, *.example, *.log, *.tar, *.gz file, and dot-files (.git*, .env). Verified: 15 sensitive URLs now return 403; index.html, assets/ (including fonts, Leaflet and onOrbitMethodology.md) and the api/ routes still return 200. The rules are on the server only: .htaccess is excluded from deploys, so they survive redeploys but are not in git. SECOND LAYER (2026-10-10, deployed): server.py now serves only index.html and files under assets/ (static_file_path(), an allowlist; paths resolved so ../ can't escape assets/), so the same files are refused locally too and a new file type can't slip through; 16 tests in 0_tests/test_server.py. STILL TO DO: (1) Proper fix: move the app root outside public_html (cPanel Python app setting, plus REMOTE_PATH in deployToGoDaddy.sh and APP_ROOT/PYTHON in setupCron.sh), so nothing is downloadable unless server.py serves it; the .htaccess rules are a blocklist, though server.py's allowlist now covers anything they miss that reaches the app. (2) GitHub repo ajg19/LCARS-FAS is public and earlier commits still contain orbitalObjects.db (Space-Track data) and space_news.db: make the repo private, or rewrite history (irreversible, force-push). (3) Delete stale leftovers on the server (deployToGoDaddy.sh, .gitignore, orbital_rocket_families-2.xlsx, server.pyc, passenger_wsgi.pyc, __pycache__): now blocked, but not needed. (4) Keep a copy of the .htaccess rules in the repo (e.g. 0_documentation) so they can be restored if cPanel rewrites the file.</t>
         </is>
       </c>
     </row>

--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -1301,23 +1301,80 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="7" t="n"/>
-      <c r="B9" s="8" t="n"/>
-      <c r="C9" s="8" t="n"/>
-      <c r="D9" s="8" t="n"/>
-      <c r="E9" s="8" t="n"/>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
+    <row r="9" ht="135" customHeight="1" s="9">
+      <c r="A9" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>GS OPS key keeps reappearing in the control panel after switching to ON-ORBIT</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Control area — assets/gsOpsPanel.js (VIS NOW status panel) / assets/onOrbitPanel.js</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>After visiting the GS OPS section and then switching to ON-ORBIT, the GS OPS key (the link-state colour key from the VIS NOW status panel) keeps popping up in the control panel, in place of ON-ORBIT's own content (the orbit regime table).</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
+        <is>
+          <t>1. Open GS OPS (VIS NOW on). 2. Click ON-ORBIT in the left menu. 3. Watch the control panel.</t>
+        </is>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>Once ON-ORBIT is open, its control panel shows only the orbit regime table; nothing from GS OPS appears.</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="inlineStr">
+        <is>
+          <t>The GS OPS key repeatedly reappears in the control panel while ON-ORBIT is open.</t>
+        </is>
+      </c>
       <c r="J9" s="8" t="n"/>
-      <c r="K9" s="2" t="n"/>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
+      <c r="K9" s="2" t="n">
+        <v>46305</v>
+      </c>
+      <c r="L9" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="M9" s="8" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="n"/>
-      <c r="O9" s="8" t="n"/>
-      <c r="Q9" s="8" t="n"/>
+      <c r="O9" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Alpha</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="Q9" s="8" t="inlineStr">
+        <is>
+          <t>Root cause not yet investigated. Unconfirmed suspect: VIS NOW's 10-second refresh timer (gsOpsPanel.js) keeps running after leaving GS OPS and redraws its status panel into #default.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n"/>

--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -1307,12 +1307,12 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>GS OPS key keeps reappearing in the control panel after switching to ON-ORBIT</t>
+          <t>GS OPS key keeps reappearing on top of other control-panel displays after GS OPS has been visited</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Open</t>
+          <t>Fixed</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
@@ -1322,30 +1322,34 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Control area — assets/gsOpsPanel.js (VIS NOW status panel) / assets/onOrbitPanel.js</t>
+          <t>Control area – assets/gsOpsPanel.js (VIS NOW status panel), affects all sections</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>After visiting the GS OPS section and then switching to ON-ORBIT, the GS OPS key (the link-state colour key from the VIS NOW status panel) keeps popping up in the control panel, in place of ON-ORBIT's own content (the orbit regime table).</t>
+          <t>Once the GS OPS section has been opened once via the LCARS spine, the GS OPS key (the link-state colour key from the VIS NOW status panel) keeps re-appearing in the control panel on top of other sections' displays (e.g. ON-ORBIT's orbit regime table). First seen with ON-ORBIT on 2026-10-10; broadened 2026-10-20: it happens with any other control-panel display.</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>1. Open GS OPS (VIS NOW on). 2. Click ON-ORBIT in the left menu. 3. Watch the control panel.</t>
+          <t>1. Open GS OPS from the LCARS spine (VIS NOW on). 2. Open any other section from the spine (e.g. ON-ORBIT). 3. Watch the control panel.</t>
         </is>
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>Once ON-ORBIT is open, its control panel shows only the orbit regime table; nothing from GS OPS appears.</t>
+          <t>After leaving GS OPS, the control panel shows only the current section's own content; nothing from GS OPS appears.</t>
         </is>
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>The GS OPS key repeatedly reappears in the control panel while ON-ORBIT is open.</t>
+          <t>The GS OPS key repeatedly reappears on top of the current section's control-panel display, in every section, for the rest of the visit.</t>
         </is>
       </c>
-      <c r="J9" s="8" t="n"/>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED (code reading only, 2026-10-20; not yet checked in the browser). gsOpsDefaultAvailable() (gsOpsPanel.js:1184) uses document.querySelector('[data-section="gs-ops"]') without the 'main ' prefix, so it matches the GS OPS spine button (index.html:64), not the section div. showSection() only sets style.display on 'main [data-section]', so the button's style.display is '' and the guard always passes. The VIS NOW refresh timer (setInterval(renderVisibleSats, 10000), gsOpsPanel.js:1345) is only cleared when VIS NOW is toggled off, not when you leave GS OPS, so every 10 s it redraws the status panel and key into #default over whichever section is open. Needs VIS NOW switched on (it starts off). Suggested fix: use 'main [data-section="gs-ops"]'; optionally also skip or pause the timer's work while GS OPS is hidden.</t>
+        </is>
+      </c>
       <c r="K9" s="2" t="n">
         <v>46305</v>
       </c>
@@ -1359,7 +1363,9 @@
           <t>Al</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n"/>
+      <c r="N9" s="2" t="n">
+        <v>46315</v>
+      </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
           <t>Pre-Alpha</t>
@@ -1372,7 +1378,7 @@
       </c>
       <c r="Q9" s="8" t="inlineStr">
         <is>
-          <t>Root cause not yet investigated. Unconfirmed suspect: VIS NOW's 10-second refresh timer (gsOpsPanel.js) keeps running after leaving GS OPS and redraws its status panel into #default.</t>
+          <t>Fixed on DEV 2026-10-20; Al checked it in the browser. (1) lcars.js: onSectionLeave(sectionId, fn) registry; showSection() runs the leave hook of the visible section when switching to a different one. (2) gsOpsPanel.js registers a gs-ops hook that turns VIS NOW off (stops the timer, clears the map layer and status panel); VIS NOW reads OFF on return. (3) Guard selector fixed to 'main [data-section="gs-ops"]' as a backstop. (4) toggleVisibleSats() no longer starts the timer if the user left GS OPS while the catalogue was loading. Related, not fixed: GRD-TRACK live-position and terminator timers also keep running while hidden; they could use the same hook.</t>
         </is>
       </c>
     </row>

--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -1382,23 +1382,86 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="7" t="n"/>
-      <c r="B10" s="8" t="n"/>
-      <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
-      <c r="E10" s="8" t="n"/>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="2" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="2" t="n"/>
-      <c r="O10" s="8" t="n"/>
-      <c r="Q10" s="8" t="n"/>
+    <row r="10" ht="135" customHeight="1" s="9">
+      <c r="A10" s="7" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>SatNOGS radio frequencies attached to SatNOGS's 9xxxx placeholder rows, not the real NORAD objects</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>Ingestion – SatNOGS radio frequencies (scripts/ingestSatnogsRf.py, now scripts/publishSite.py); affects link budget and object details</t>
+        </is>
+      </c>
+      <c r="F10" s="8" t="inlineStr">
+        <is>
+          <t>SatNOGS radio frequencies (downlink/uplink, bandwidth, mode, baud) were attached to SatNOGS's duplicate rows under its own 98xxx/99xxx placeholder numbers instead of the real NORAD objects. Those NORAD objects therefore had no real frequencies, and the link budget fell back to band mid-points for them. On LIVE, 384 satellites' frequencies sat on 9xxxx duplicates (of 1,677 with SatNOGS frequencies).</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>1. On the pre-refactor data, query orbital_objects for rows with rfSource = 'satnogs' and noradID &gt;= 90000. 2. Look up the real NORAD object with the same international designator (e.g. SatNOGS 98193 JACK-007 = 2026-229K). 3. Compare their frequency columns.</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Each satellite's SatNOGS frequencies are on its NORAD object, and SatNOGS's placeholder numbers never appear as separate objects.</t>
+        </is>
+      </c>
+      <c r="I10" s="8" t="inlineStr">
+        <is>
+          <t>Frequencies sat on the placeholder duplicate rows; the real NORAD objects had none.</t>
+        </is>
+      </c>
+      <c r="J10" s="8" t="inlineStr">
+        <is>
+          <t>The old pipeline (ingestOrbitalData.py) stored SatNOGS TLE rows as orbital objects under SatNOGS's placeholder numbers, and ingestSatnogsRf.py attached RF by the transmitter's norad_cat_id, which for satellites launched since NORAD's 5-digit numbers ran out (July 2026) is the placeholder, not the NORAD number.</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="L10" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="M10" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>46316</v>
+      </c>
+      <c r="O10" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Alpha</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="Q10" s="8" t="inlineStr">
+        <is>
+          <t>Fixed by the database refactor (0_documentation/dbRefactorPlan.md, step 9): orbits come from Space-Track only, SatNOGS's TLE feed is kept only as an ID crosswalk, and publishSite.py links each transmitter by norad_follow_id, then the designator in SatNOGS's TLE matched to Space-Track's objectID, then its own norad_cat_id. After: 1,433 satellites with SatNOGS frequencies, none on 9xxxx duplicates. Live on LIVE since the migration, 2026-10-21 23:04 UTC. Covered by 0_tests/test_publishSite.py.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>

--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -1463,23 +1463,86 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="8" t="n"/>
-      <c r="C11" s="8" t="n"/>
-      <c r="D11" s="8" t="n"/>
-      <c r="E11" s="8" t="n"/>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="8" t="n"/>
-      <c r="I11" s="8" t="n"/>
-      <c r="J11" s="8" t="n"/>
-      <c r="K11" s="2" t="n"/>
-      <c r="L11" s="8" t="n"/>
-      <c r="M11" s="8" t="n"/>
-      <c r="N11" s="2" t="n"/>
-      <c r="O11" s="8" t="n"/>
-      <c r="Q11" s="8" t="n"/>
+    <row r="11" ht="135" customHeight="1" s="9">
+      <c r="A11" s="7" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Site .db.prev files and databases/.writers.lock downloadable after DB refactor (bug 7 regression)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Fixed</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>Live web server – .htaccess (server-only rewrite rules); databases/</t>
+        </is>
+      </c>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>After the database refactor moved the databases to databases/ and added .prev copies and a lock file, the live web server served some of them: databases/siteOrbital.db.prev and siteNews.db.prev (site databases, including Space-Track-derived data) and databases/.writers.lock returned 200. databases/siteOrbital.db itself was refused (403). A regression of bug 7.</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
+        <is>
+          <t>1. curl -I https://gaps2024.com/LCARS-FAS/databases/siteOrbital.db.prev 2. Same for databases/siteNews.db.prev and databases/.writers.lock.</t>
+        </is>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>403 for every file under databases/ and every dot-file.</t>
+        </is>
+      </c>
+      <c r="I11" s="8" t="inlineStr">
+        <is>
+          <t>200 for the .db.prev files and .writers.lock (403 only for *.db).</t>
+        </is>
+      </c>
+      <c r="J11" s="8" t="inlineStr">
+        <is>
+          <t>The server-only .htaccess block list named the old folder ingestionDBs/ and the .db extension, but not databases/, the .prev/.tmp/.lock extensions or dot-files. The refactor added all of these without updating it.</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="L11" s="8" t="inlineStr">
+        <is>
+          <t>LIVE</t>
+        </is>
+      </c>
+      <c r="M11" s="8" t="inlineStr">
+        <is>
+          <t>Claude</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>46317</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Alpha</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="Q11" s="8" t="inlineStr">
+        <is>
+          <t>Found by the DB refactor step 14 (documentation) session with HEAD requests. Fixed on LIVE 2026-10-22 ~11:55 UTC with Al's go-ahead: the folder rule adds databases/, the extension rule adds prev|tmp|new|lock|objects, and the dot-file rule is now (^|/)\. (covers .writers.lock, .referenceUpload/, .deployStage/). Backup: ~/backups/LCARS-FAS.htaccess.pre-dbRefactor-20261022-115511. Verified: siteOrbital.db, .db.prev, .db.tmp, .writers.lock and ingestionDBs/ return 403; pages and APIs 200. Regression guard: 0_tools/liveCheck.py privacy section, 15 private paths (commit 3800497). The .htaccess is a block list: any new file type or folder under the app root must be added to it and to liveCheck's privacy list.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n"/>

--- a/bugsDB.xlsx
+++ b/bugsDB.xlsx
@@ -1544,23 +1544,84 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="n"/>
-      <c r="B12" s="8" t="n"/>
-      <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
-      <c r="E12" s="8" t="n"/>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="2" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
+    <row r="12" ht="135" customHeight="1" s="9">
+      <c r="A12" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Control panel scrolled off the top of the screen after clicking a spine button</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E12" s="8" t="inlineStr">
+        <is>
+          <t>Spine navigation: assets/lcars.js showSection(); seen on EO</t>
+        </is>
+      </c>
+      <c r="F12" s="8" t="inlineStr">
+        <is>
+          <t>After clicking a spine button the new section loads, but the page is scrolled so that the control panel at the top is off the top of the screen. Intermittent: it does not happen every time. Definitely reproduced on the EO screen.</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>1. Open a section and scroll down the page, or use a tall section. 2. Click another button on the spine, for example EO. 3. Look at the top of the page.</t>
+        </is>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>Each spine click shows the new section with the control panel (and banner) visible at the top of the page.</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="inlineStr">
+        <is>
+          <t>The section's main content loads but the page stays scrolled down, leaving the control panel above the visible area.</t>
+        </is>
+      </c>
+      <c r="J12" s="8" t="inlineStr">
+        <is>
+          <t>UNCONFIRMED: showSection() does not reset the scroll position. topFunction() (which scrolls to the top) is called from only two places in lcars.js, so most spine buttons keep whatever scroll position the previous section left. Map sections (EO) may also scroll the page when the map initialises. Not yet investigated.</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>46319</v>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>DEV</t>
+        </is>
+      </c>
+      <c r="M12" s="8" t="inlineStr">
+        <is>
+          <t>Al</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="Q12" s="8" t="n"/>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>Pre-Alpha</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="inlineStr">
+        <is>
+          <t>Bug</t>
+        </is>
+      </c>
+      <c r="Q12" s="8" t="inlineStr">
+        <is>
+          <t>Fix applied 2026-10-24: showSection() now scrolls to the top on every section change. Awaiting Al's test on DEV; not yet marked Fixed. If it still happens on EO, suspect the map initialising and scrolling the page after showSection() has run.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n"/>
